--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484340_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484340_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>D. TORRALBA CAROZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.623</v>
+        <v>0.4495</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.155</v>
+        <v>0.4286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.778</v>
+        <v>0.0209</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6073</v>
+        <v>0.3924</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4587</v>
+        <v>0.1228</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1486</v>
+        <v>0.2696</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6422</v>
+        <v>0.3275</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7188</v>
+        <v>0.3275</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0349</v>
+        <v>0.065</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1775</v>
+        <v>-0.2047</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2124</v>
+        <v>0.2696</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0433</v>
+        <v>0.0571</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4722</v>
+        <v>0.1011</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4289</v>
+        <v>-0.044</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. TORRALBA CAROZ</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2334</v>
+        <v>0.1657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2669</v>
+        <v>1.6137</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0335</v>
+        <v>-1.448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3924</v>
+        <v>-1.3943</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1228</v>
+        <v>-0.2469</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2696</v>
+        <v>-1.1475</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3275</v>
+        <v>0.5336</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3275</v>
+        <v>1.6795</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.1459</v>
       </c>
       <c r="M3" t="n">
-        <v>0.065</v>
+        <v>-1.9279</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2047</v>
+        <v>-1.9263</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2696</v>
+        <v>-0.0016</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.159</v>
+        <v>-1.0531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0605</v>
+        <v>-0.1656</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0985</v>
+        <v>-0.8875</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2641</v>
+        <v>-0.1266</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5406</v>
+        <v>-0.823</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8047</v>
+        <v>0.6963</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2382</v>
+        <v>-0.6073</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1914</v>
+        <v>-0.4587</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4295</v>
+        <v>-0.1486</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7967</v>
+        <v>-0.6422</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2878</v>
+        <v>0.7188</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5089</v>
+        <v>-1.361</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5585</v>
+        <v>0.0349</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4792</v>
+        <v>-1.1775</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0793</v>
+        <v>1.2124</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1348</v>
+        <v>0.2936</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3026</v>
+        <v>0.8042</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1678</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6577</v>
+        <v>-0.1629</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9265</v>
+        <v>0.6417</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5842</v>
+        <v>-0.8047</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3943</v>
+        <v>1.2382</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2469</v>
+        <v>-0.1914</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1475</v>
+        <v>1.4295</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5336</v>
+        <v>2.7967</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6795</v>
+        <v>0.2878</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1459</v>
+        <v>2.5089</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9279</v>
+        <v>-1.5585</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9263</v>
+        <v>-0.4792</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0016</v>
+        <v>-1.0793</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8764</v>
+        <v>-0.0337</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8527</v>
+        <v>-0.2015</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0237</v>
+        <v>0.1678</v>
       </c>
       <c r="V5" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7721</v>
+        <v>-0.4027</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7065</v>
+        <v>0.4348</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4786</v>
+        <v>-0.8375</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4795</v>
+        <v>-1.6322</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6946</v>
+        <v>-1.2134</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1741</v>
+        <v>-0.4189</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6982</v>
+        <v>-1.2627</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6577</v>
+        <v>-0.0359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-1.2268</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1777</v>
+        <v>-0.3696</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.1775</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2146</v>
+        <v>0.8079</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1288</v>
+        <v>-0.7622</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0083</v>
+        <v>0.2918</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1371</v>
+        <v>-1.0539</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5545</v>
+        <v>2.3824</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8627</v>
+        <v>-0.8089</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1927</v>
+        <v>-0.6816</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0554</v>
+        <v>-0.1273</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6322</v>
+        <v>-0.1079</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2134</v>
+        <v>-1.0379</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4189</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2627</v>
+        <v>0.1918</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0359</v>
+        <v>0.2047</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2268</v>
+        <v>-0.0128</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3696</v>
+        <v>-0.2998</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1775</v>
+        <v>-1.2425</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8079</v>
+        <v>0.9428</v>
       </c>
       <c r="P7" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2221</v>
+        <v>-0.0331</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0497</v>
+        <v>0.2987</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2718</v>
+        <v>-0.3317</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3824</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5215</v>
+        <v>-0.8339</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5304</v>
+        <v>1.7265</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008800000000000001</v>
+        <v>-2.5603</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1079</v>
+        <v>-0.4795</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0379</v>
+        <v>0.6946</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9298999999999999</v>
+        <v>-1.1741</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1918</v>
+        <v>1.6982</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2047</v>
+        <v>1.6577</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0128</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2998</v>
+        <v>-2.1777</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2425</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9428</v>
+        <v>-1.2146</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7457</v>
+        <v>-0.1905</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5501</v>
+        <v>0.0283</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1956</v>
+        <v>-0.2188</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6785</v>
+        <v>-2.1684</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1071</v>
+        <v>-0.6008</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7855</v>
+        <v>-1.5676</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8555</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>0.591</v>
+        <v>0.1011</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9245</v>
+        <v>0.2167</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3335</v>
+        <v>-0.1156</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.748</v>
+        <v>-2.9659</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3938</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3542</v>
+        <v>-2.5721</v>
       </c>
       <c r="G10" t="n">
         <v>1.1192</v>
@@ -1234,13 +1234,13 @@
         <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0655</v>
+        <v>-0.2834</v>
       </c>
       <c r="T10" t="n">
         <v>0.0221</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0877</v>
+        <v>-0.3055</v>
       </c>
       <c r="V10" t="n">
         <v>0.8865</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2252</v>
+        <v>-3.2777</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6609</v>
+        <v>-1.6555</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5644</v>
+        <v>-1.6222</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7955</v>
+        <v>-0.0184</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2559</v>
+        <v>-2.1487</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5397</v>
+        <v>2.1303</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9814</v>
+        <v>1.5004</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9814</v>
+        <v>-1.0361</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5365</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8142</v>
+        <v>-1.5188</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2745</v>
+        <v>-1.1125</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5397</v>
+        <v>-0.4062</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.547</v>
+        <v>-1.091</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4925</v>
+        <v>-0.2062</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0545</v>
+        <v>-0.8848</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5581</v>
+        <v>-3.3458</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.181</v>
+        <v>-2.8631</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3771</v>
+        <v>-0.4827</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0184</v>
+        <v>-2.7955</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1487</v>
+        <v>-2.2559</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1303</v>
+        <v>-0.5397</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5004</v>
+        <v>-1.9814</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0361</v>
+        <v>-1.9814</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5365</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5188</v>
+        <v>-0.8142</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1125</v>
+        <v>-0.2745</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4062</v>
+        <v>-0.5397</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3714</v>
+        <v>0.4265</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7317</v>
+        <v>0.2903</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6397</v>
+        <v>0.1362</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.789</v>
+        <v>-3.5323</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4484</v>
+        <v>-1.2461</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3406</v>
+        <v>-2.2861</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3508</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2196</v>
+        <v>0.0371</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1816</v>
+        <v>0.0207</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.038</v>
+        <v>0.0165</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2186</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.2205</v>
+        <v>-17.0099</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.629199999999999</v>
+        <v>-3.4186</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.5914</v>
+        <v>-13.5913</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.4916</v>
+        <v>-9.491599999999998</v>
       </c>
       <c r="H14" t="n">
         <v>-8.1378</v>
@@ -1537,7 +1537,7 @@
         <v>-3.3823</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.813700000000001</v>
+        <v>-7.8137</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.6507</v>
@@ -1546,13 +1546,13 @@
         <v>6.836999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.742</v>
+        <v>-2.5316</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2900999999999998</v>
+        <v>1.5006</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.0322</v>
+        <v>-4.0319</v>
       </c>
       <c r="V14" t="n">
         <v>2.8272</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1035</v>
+        <v>5.9928</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1506</v>
+        <v>3.8817</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9529</v>
+        <v>2.1111</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3422</v>
+        <v>4.8735</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8683</v>
+        <v>1.0821</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5261</v>
+        <v>3.7913</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1764</v>
+        <v>3.4751</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0274</v>
+        <v>0.4924</v>
       </c>
       <c r="L15" t="n">
-        <v>0.149</v>
+        <v>2.9826</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8342000000000001</v>
+        <v>1.3984</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1591</v>
+        <v>0.5897</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6751</v>
+        <v>0.8087</v>
       </c>
       <c r="P15" t="n">
         <v>1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3939</v>
+        <v>0.5799</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5602</v>
+        <v>0.4067</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1663</v>
+        <v>0.1732</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8298</v>
+        <v>5.4713</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9282</v>
+        <v>5.0727</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0984</v>
+        <v>0.3986</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4608</v>
+        <v>5.7689</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5257</v>
+        <v>2.2078</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0649</v>
+        <v>3.5612</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0152</v>
+        <v>5.8588</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5403</v>
+        <v>2.0274</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5251</v>
+        <v>3.8314</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5544</v>
+        <v>-0.0898</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0146</v>
+        <v>0.1804</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5399</v>
+        <v>-0.2702</v>
       </c>
       <c r="P16" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.3674</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.5627</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.3337</v>
+        <v>0.7256</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6124</v>
+        <v>0.386</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.3397</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7363</v>
+        <v>4.9622</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7694</v>
+        <v>3.4428</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0331</v>
+        <v>1.5194</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7689</v>
+        <v>1.3422</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2078</v>
+        <v>1.8683</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5612</v>
+        <v>-0.5261</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8588</v>
+        <v>2.1764</v>
       </c>
       <c r="K17" t="n">
         <v>2.0274</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8314</v>
+        <v>0.149</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0898</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1804</v>
+        <v>-0.1591</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2702</v>
+        <v>-0.6751</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0094</v>
+        <v>1.2526</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.8524</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.092</v>
+        <v>0.4002</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5122</v>
+        <v>3.6007</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3761</v>
+        <v>3.917</v>
       </c>
       <c r="F18" t="n">
-        <v>1.136</v>
+        <v>-0.3163</v>
       </c>
       <c r="G18" t="n">
-        <v>4.8735</v>
+        <v>1.4608</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0821</v>
+        <v>2.5257</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7913</v>
+        <v>-1.0649</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4751</v>
+        <v>2.0152</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4924</v>
+        <v>2.5403</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9826</v>
+        <v>-0.5251</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3984</v>
+        <v>-0.5544</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5897</v>
+        <v>-0.0146</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8087</v>
+        <v>-0.5399</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9006999999999999</v>
+        <v>1.1046</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0989</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8018</v>
+        <v>0.5034</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6489</v>
+        <v>2.4791</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4604</v>
+        <v>0.157</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1886</v>
+        <v>2.322</v>
       </c>
       <c r="G19" t="n">
         <v>0.2023</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2904</v>
+        <v>1.1205</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2355</v>
+        <v>0.9322</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0549</v>
+        <v>0.1883</v>
       </c>
       <c r="V19" t="n">
         <v>1.9376</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1334</v>
+        <v>1.8975</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.2651</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3627</v>
+        <v>1.6324</v>
       </c>
       <c r="G20" t="n">
         <v>1.5198</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6136</v>
+        <v>0.3776</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6219</v>
+        <v>0.1164</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0083</v>
+        <v>0.2613</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9217</v>
+        <v>1.6882</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1749</v>
+        <v>0.9727</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7468</v>
+        <v>0.7155</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8781</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7097</v>
+        <v>1.4761</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8118</v>
+        <v>0.6096</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8978</v>
+        <v>0.8665</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5048</v>
+        <v>-0.985</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2735</v>
+        <v>0.5769</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7784</v>
+        <v>-1.5618</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0285</v>
@@ -2170,13 +2170,13 @@
         <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4297</v>
+        <v>0.0902</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2037</v>
+        <v>0.507</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6334</v>
+        <v>-0.4169</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5651</v>
+        <v>-1.1286</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8652</v>
+        <v>-2.2694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3001</v>
+        <v>1.1409</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5029</v>
+        <v>-2.3155</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3576</v>
+        <v>-1.4132</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1453</v>
+        <v>-0.9023</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9436</v>
+        <v>-1.4167</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2034</v>
+        <v>-0.6498</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7402</v>
+        <v>-0.7669</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5593</v>
+        <v>-0.8988</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1542</v>
+        <v>-0.7634</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4051</v>
+        <v>-0.1354</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0389</v>
+        <v>0.2958</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3126</v>
+        <v>0.1719</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9826</v>
+        <v>-1.1528</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9644</v>
+        <v>-1.5619</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0182</v>
+        <v>0.4091</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0493</v>
+        <v>-1.5029</v>
       </c>
       <c r="H24" t="n">
-        <v>1.317</v>
+        <v>-0.3576</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2677</v>
+        <v>-1.1453</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3892</v>
+        <v>-0.9436</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.2034</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7402</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3399</v>
+        <v>-0.5593</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3346</v>
+        <v>-0.1542</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6745</v>
+        <v>-0.4051</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0319</v>
+        <v>-0.6266</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1816</v>
+        <v>-0.4229</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1496</v>
+        <v>-0.2037</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>I. MACÍAS MERINO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6129</v>
+        <v>-1.9087</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4828</v>
+        <v>-0.8633</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8699</v>
+        <v>-1.0454</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3155</v>
+        <v>0.0493</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4132</v>
+        <v>1.317</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9023</v>
+        <v>-1.2677</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4167</v>
+        <v>0.3892</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6498</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7669</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8988</v>
+        <v>-0.3399</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7634</v>
+        <v>0.3346</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1354</v>
+        <v>-0.6745</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1885</v>
+        <v>0.0419</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0894</v>
+        <v>-0.0805</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.1224</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>18.2204</v>
+        <v>20.9167</v>
       </c>
       <c r="E26" t="n">
-        <v>13.5914</v>
+        <v>13.5913</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6289</v>
+        <v>7.325500000000001</v>
       </c>
       <c r="G26" t="n">
         <v>9.4918</v>
@@ -2473,22 +2473,22 @@
         <v>-2.0283</v>
       </c>
       <c r="P26" t="n">
-        <v>7.8137</v>
+        <v>7.813699999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-6.836899999999999</v>
+        <v>-6.8369</v>
       </c>
       <c r="R26" t="n">
         <v>14.6508</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7422</v>
+        <v>6.4382</v>
       </c>
       <c r="T26" t="n">
-        <v>4.031899999999998</v>
+        <v>4.0322</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2898999999999998</v>
+        <v>2.4063</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8271</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484340_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484340_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1657</v>
+        <v>0.307</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6137</v>
+        <v>0.307</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.448</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3943</v>
+        <v>0.307</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2469</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1475</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5336</v>
+        <v>0.307</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6795</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1459</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9279</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9263</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0016</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0531</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1656</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8875</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1266</v>
+        <v>0.1657</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.823</v>
+        <v>1.6137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6963</v>
+        <v>-1.448</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6073</v>
+        <v>-1.3943</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4587</v>
+        <v>-0.2469</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1486</v>
+        <v>-1.1475</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6422</v>
+        <v>0.5336</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7188</v>
+        <v>1.6795</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.361</v>
+        <v>-1.1459</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0349</v>
+        <v>-1.9279</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1775</v>
+        <v>-1.9263</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2124</v>
+        <v>-0.0016</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2936</v>
+        <v>-1.0531</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8042</v>
+        <v>-0.1656</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.8875</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1638</v>
+        <v>1.441</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1638</v>
+        <v>1.441</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1629</v>
+        <v>-0.1266</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6417</v>
+        <v>-0.823</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8047</v>
+        <v>0.6963</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2382</v>
+        <v>-0.6073</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1914</v>
+        <v>-0.4587</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4295</v>
+        <v>-0.1486</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7967</v>
+        <v>-0.6422</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2878</v>
+        <v>0.7188</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5089</v>
+        <v>-1.361</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5585</v>
+        <v>0.0349</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4792</v>
+        <v>-1.1775</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0793</v>
+        <v>1.2124</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0337</v>
+        <v>0.2936</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2015</v>
+        <v>0.8042</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1678</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4027</v>
+        <v>-0.1629</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4348</v>
+        <v>0.6417</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8375</v>
+        <v>-0.8047</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6322</v>
+        <v>1.2382</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2134</v>
+        <v>-0.1914</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4189</v>
+        <v>1.4295</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2627</v>
+        <v>2.7967</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0359</v>
+        <v>0.2878</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2268</v>
+        <v>2.5089</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3696</v>
+        <v>-1.5585</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1775</v>
+        <v>-0.4792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8079</v>
+        <v>-1.0793</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7622</v>
+        <v>-0.0337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2918</v>
+        <v>-0.2015</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0539</v>
+        <v>0.1678</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8089</v>
+        <v>-0.4027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6816</v>
+        <v>0.4348</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1273</v>
+        <v>-0.8375</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1079</v>
+        <v>-1.6322</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0379</v>
+        <v>-1.2134</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9298999999999999</v>
+        <v>-0.4189</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1918</v>
+        <v>-1.2627</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2047</v>
+        <v>-0.0359</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0128</v>
+        <v>-1.2268</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2998</v>
+        <v>-0.3696</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2425</v>
+        <v>-1.1775</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9428</v>
+        <v>0.8079</v>
       </c>
       <c r="P7" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0331</v>
+        <v>-0.7622</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2987</v>
+        <v>0.2918</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3317</v>
+        <v>-1.0539</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>2.3824</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8339</v>
+        <v>-0.8089</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7265</v>
+        <v>-0.6816</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5603</v>
+        <v>-0.1273</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4795</v>
+        <v>-0.1079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6946</v>
+        <v>-1.0379</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1741</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6982</v>
+        <v>0.1918</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6577</v>
+        <v>0.2047</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>-0.0128</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1777</v>
+        <v>-0.2998</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.2425</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2146</v>
+        <v>0.9428</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1905</v>
+        <v>-0.0331</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0283</v>
+        <v>0.2987</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2188</v>
+        <v>-0.3317</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1684</v>
+        <v>-0.8339</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6008</v>
+        <v>1.7265</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5676</v>
+        <v>-2.5603</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8555</v>
+        <v>-0.4795</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6275</v>
+        <v>0.6946</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.228</v>
+        <v>-1.1741</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8175</v>
+        <v>1.6982</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9389</v>
+        <v>1.6577</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1214</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.038</v>
+        <v>-2.1777</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6887</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3494</v>
+        <v>-1.2146</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1011</v>
+        <v>-0.1905</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2167</v>
+        <v>0.0283</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1156</v>
+        <v>-0.2188</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9659</v>
+        <v>-2.4754</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3938</v>
+        <v>-0.9077</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5721</v>
+        <v>-1.5676</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1192</v>
+        <v>-3.1625</v>
       </c>
       <c r="H10" t="n">
-        <v>0.998</v>
+        <v>-1.9345</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1212</v>
+        <v>-1.228</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1671</v>
+        <v>-1.1245</v>
       </c>
       <c r="K10" t="n">
-        <v>1.966</v>
+        <v>-1.2459</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2011</v>
+        <v>0.1214</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.048</v>
+        <v>-2.038</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.968</v>
+        <v>-0.6887</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0799</v>
+        <v>-1.3494</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.6882</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0789</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2834</v>
+        <v>0.1011</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0221</v>
+        <v>0.2167</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3055</v>
+        <v>-0.1156</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2777</v>
+        <v>-2.9659</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6555</v>
+        <v>-0.3938</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6222</v>
+        <v>-2.5721</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0184</v>
+        <v>1.1192</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1487</v>
+        <v>0.998</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1303</v>
+        <v>0.1212</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5004</v>
+        <v>3.1671</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0361</v>
+        <v>1.966</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5365</v>
+        <v>1.2011</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5188</v>
+        <v>-2.048</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1125</v>
+        <v>-0.968</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4062</v>
+        <v>-1.0799</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1721</v>
+        <v>-4.6882</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-5.0789</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.091</v>
+        <v>-0.2834</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2062</v>
+        <v>0.0221</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8848</v>
+        <v>-0.3055</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9962</v>
+        <v>0.8865</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.9962</v>
+        <v>1.4959</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3458</v>
+        <v>-3.2777</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8631</v>
+        <v>-1.6555</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4827</v>
+        <v>-1.6222</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7955</v>
+        <v>-0.0184</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2559</v>
+        <v>-2.1487</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5397</v>
+        <v>2.1303</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9814</v>
+        <v>1.5004</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9814</v>
+        <v>-1.0361</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.5365</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8142</v>
+        <v>-1.5188</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2745</v>
+        <v>-1.1125</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5397</v>
+        <v>-0.4062</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4265</v>
+        <v>-1.091</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2903</v>
+        <v>-0.2062</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1362</v>
+        <v>-0.8848</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5323</v>
+        <v>-3.3458</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2461</v>
+        <v>-2.8631</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2861</v>
+        <v>-0.4827</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3508</v>
+        <v>-2.7955</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7728</v>
+        <v>-2.2559</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.578</v>
+        <v>-0.5397</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2668</v>
+        <v>-1.9814</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6332</v>
+        <v>-1.9814</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.084</v>
+        <v>-0.8142</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1397</v>
+        <v>-0.2745</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9443</v>
+        <v>-0.5397</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0371</v>
+        <v>0.4265</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0207</v>
+        <v>0.2903</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0165</v>
+        <v>0.1362</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.0099</v>
+        <v>-3.5323</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.4186</v>
+        <v>-1.2461</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.5913</v>
+        <v>-2.2861</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.491599999999998</v>
+        <v>-2.3508</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.1378</v>
+        <v>-0.7728</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3543</v>
+        <v>-1.578</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2447</v>
+        <v>-1.2668</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2165</v>
+        <v>-0.6332</v>
       </c>
       <c r="L14" t="n">
-        <v>2.028300000000001</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.7366</v>
+        <v>-1.084</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.3543</v>
+        <v>-0.1397</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.3823</v>
+        <v>-0.9443</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.8137</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.6507</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6.836999999999999</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5316</v>
+        <v>0.0371</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5006</v>
+        <v>0.0207</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.0319</v>
+        <v>0.0165</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8272</v>
+        <v>-1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>5.486899999999999</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6596</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9928</v>
+        <v>-17.0099</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8817</v>
+        <v>-3.4185</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1111</v>
+        <v>-13.5913</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8735</v>
+        <v>-9.491599999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0821</v>
+        <v>-8.1378</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7913</v>
+        <v>-1.3543</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4751</v>
+        <v>4.2447</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4924</v>
+        <v>2.2165</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9826</v>
+        <v>2.028300000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3984</v>
+        <v>-13.7366</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5897</v>
+        <v>-10.3543</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8087</v>
+        <v>-3.3823</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>-7.8137</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-14.6507</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>6.836999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5799</v>
+        <v>-2.5316</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4067</v>
+        <v>1.5006</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1732</v>
+        <v>-4.031900000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>2.8272</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.486899999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-2.6596</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4713</v>
+        <v>5.9928</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0727</v>
+        <v>3.8817</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3986</v>
+        <v>2.1111</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7689</v>
+        <v>4.8735</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2078</v>
+        <v>1.0821</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5612</v>
+        <v>3.7913</v>
       </c>
       <c r="J16" t="n">
-        <v>5.8588</v>
+        <v>3.4751</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0274</v>
+        <v>0.4924</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8314</v>
+        <v>2.9826</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0898</v>
+        <v>1.3984</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1804</v>
+        <v>0.5897</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2702</v>
+        <v>0.8087</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7256</v>
+        <v>0.5799</v>
       </c>
       <c r="T16" t="n">
-        <v>0.386</v>
+        <v>0.4067</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3397</v>
+        <v>0.1732</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1718,6 +1789,11 @@
       </c>
       <c r="X16" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1797,11 +1873,16 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6007</v>
+        <v>4.2559</v>
       </c>
       <c r="E18" t="n">
-        <v>3.917</v>
+        <v>4.2559</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3163</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4608</v>
+        <v>4.2559</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5257</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0649</v>
+        <v>3.6419</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0152</v>
+        <v>4.2559</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5403</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5251</v>
+        <v>3.6419</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5544</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0146</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1046</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6012999999999999</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5034</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4791</v>
+        <v>3.6007</v>
       </c>
       <c r="E19" t="n">
-        <v>0.157</v>
+        <v>3.917</v>
       </c>
       <c r="F19" t="n">
-        <v>2.322</v>
+        <v>-0.3163</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2023</v>
+        <v>1.4608</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3502</v>
+        <v>2.5257</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5525</v>
+        <v>-1.0649</v>
       </c>
       <c r="J19" t="n">
-        <v>0.901</v>
+        <v>2.0152</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6178</v>
+        <v>2.5403</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2833</v>
+        <v>-0.5251</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6988</v>
+        <v>-0.5544</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.968</v>
+        <v>-0.0146</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2692</v>
+        <v>-0.5399</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1205</v>
+        <v>1.1046</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9322</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1883</v>
+        <v>0.5034</v>
       </c>
       <c r="V19" t="n">
-        <v>1.9376</v>
+        <v>-0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
-        <v>1.6604</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8975</v>
+        <v>2.4791</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2651</v>
+        <v>0.157</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6324</v>
+        <v>2.322</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5198</v>
+        <v>0.2023</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3988</v>
+        <v>-0.3502</v>
       </c>
       <c r="I20" t="n">
-        <v>0.121</v>
+        <v>0.5525</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1255</v>
+        <v>0.901</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0041</v>
+        <v>0.6178</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>0.2833</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3944</v>
+        <v>-0.6988</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3948</v>
+        <v>-0.968</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0004</v>
+        <v>0.2692</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3776</v>
+        <v>1.1205</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1164</v>
+        <v>0.9322</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2613</v>
+        <v>0.1883</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.9376</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.6604</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6882</v>
+        <v>1.8975</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9727</v>
+        <v>0.2651</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7155</v>
+        <v>1.6324</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8781</v>
+        <v>1.5198</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1059</v>
+        <v>1.3988</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.984</v>
+        <v>0.121</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0859</v>
+        <v>1.1255</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7994</v>
+        <v>1.0041</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7136</v>
+        <v>0.1214</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9639</v>
+        <v>0.3944</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6935</v>
+        <v>0.3948</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2704</v>
+        <v>-0.0004</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4761</v>
+        <v>0.3776</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6096</v>
+        <v>0.1164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8665</v>
+        <v>0.2613</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.985</v>
+        <v>1.6882</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5769</v>
+        <v>0.9727</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5618</v>
+        <v>0.7155</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0285</v>
+        <v>-0.8781</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2469</v>
+        <v>0.1059</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7817</v>
+        <v>-0.984</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0698</v>
+        <v>0.0859</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7163</v>
+        <v>0.7994</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6465</v>
+        <v>-0.7136</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0984</v>
+        <v>-0.9639</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.6935</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1352</v>
+        <v>-0.2704</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0902</v>
+        <v>1.4761</v>
       </c>
       <c r="T22" t="n">
-        <v>0.507</v>
+        <v>0.6096</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4169</v>
+        <v>0.8665</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1286</v>
+        <v>1.2154</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2694</v>
+        <v>0.8168</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1409</v>
+        <v>0.3986</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3155</v>
+        <v>1.5131</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4132</v>
+        <v>1.5938</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9023</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4167</v>
+        <v>1.6029</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6498</v>
+        <v>1.4134</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7669</v>
+        <v>0.1895</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8988</v>
+        <v>-0.0898</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7634</v>
+        <v>0.1804</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1354</v>
+        <v>-0.2702</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2958</v>
+        <v>0.7256</v>
       </c>
       <c r="T23" t="n">
-        <v>0.124</v>
+        <v>0.386</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1719</v>
+        <v>0.3397</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1528</v>
+        <v>-0.985</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5619</v>
+        <v>0.5769</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4091</v>
+        <v>-1.5618</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5029</v>
+        <v>-1.0285</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3576</v>
+        <v>-0.2469</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1453</v>
+        <v>-0.7817</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9436</v>
+        <v>0.0698</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2034</v>
+        <v>0.7163</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7402</v>
+        <v>-0.6465</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5593</v>
+        <v>-1.0984</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1542</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4051</v>
+        <v>-0.1352</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6266</v>
+        <v>0.0902</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4229</v>
+        <v>0.507</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2037</v>
+        <v>-0.4169</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9087</v>
+        <v>-1.1286</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8633</v>
+        <v>-2.2694</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0454</v>
+        <v>1.1409</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0493</v>
+        <v>-2.3155</v>
       </c>
       <c r="H25" t="n">
-        <v>1.317</v>
+        <v>-1.4132</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2677</v>
+        <v>-0.9023</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3892</v>
+        <v>-1.4167</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.6498</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7669</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3399</v>
+        <v>-0.8988</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3346</v>
+        <v>-0.7634</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6745</v>
+        <v>-0.1354</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0419</v>
+        <v>0.2958</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0805</v>
+        <v>0.124</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1224</v>
+        <v>0.1719</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2186</v>
+        <v>0.1097</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2186</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-1.1528</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.5619</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.5029</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.3576</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.1453</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.9436</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.2034</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.7402</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.5593</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.1542</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.6266</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.4229</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.2037</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I. MACIAS MERINO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.9087</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.8633</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.0454</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.2677</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.3399</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.0805</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484340_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>20.9167</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>13.5913</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>7.325500000000001</v>
       </c>
-      <c r="G26" t="n">
-        <v>9.4918</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G28" t="n">
+        <v>9.491900000000001</v>
+      </c>
+      <c r="H28" t="n">
         <v>8.137700000000001</v>
       </c>
-      <c r="I26" t="n">
-        <v>1.354</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="I28" t="n">
+        <v>1.354000000000001</v>
+      </c>
+      <c r="J28" t="n">
         <v>13.7366</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K28" t="n">
         <v>10.3543</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L28" t="n">
         <v>3.382200000000001</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>-4.2447</v>
       </c>
-      <c r="N26" t="n">
-        <v>-2.216499999999999</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="N28" t="n">
+        <v>-2.2165</v>
+      </c>
+      <c r="O28" t="n">
         <v>-2.0283</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>7.813699999999999</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-6.8369</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>14.6508</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>6.4382</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>4.0322</v>
       </c>
-      <c r="U26" t="n">
-        <v>2.4063</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="U28" t="n">
+        <v>2.406299999999999</v>
+      </c>
+      <c r="V28" t="n">
         <v>-2.8271</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>2.6596</v>
       </c>
-      <c r="X26" t="n">
-        <v>-5.486700000000001</v>
-      </c>
+      <c r="X28" t="n">
+        <v>-5.486699999999999</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
